--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/desktop/desktop_quick_view.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/desktop/desktop_quick_view.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="C2" t="n">
-        <v>48</v>
+        <v>47.77</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>32.5</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>16.96</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
     </row>
   </sheetData>
